--- a/testdata/005930.xlsx
+++ b/testdata/005930.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jinuchoi\projects\PB_AI\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31103A88-CED0-48AD-90AB-403F9F5E810A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D43A54-36C5-447D-9184-07FDDC2D9000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-1402" windowWidth="21795" windowHeight="12974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2587,7 +2587,8 @@
   <dimension ref="A1:S214"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="36.75" customWidth="1"/>
+    <col min="8" max="8" width="16.625" customWidth="1"/>
+    <col min="9" max="9" width="39.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
